--- a/reports/pdf_rolling5_20260911.xlsx
+++ b/reports/pdf_rolling5_20260911.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,595억   ·   현금 47억(1.0%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 15종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,659억   ·   현금 31억(0.7%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 15종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>935</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6727624200</v>
+        <v>6681089250</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1540770000</v>
+        <v>-1530112500</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>116</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>451959200</v>
+        <v>448833000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-43</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-308528440</v>
+        <v>-306394350</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3588248400</v>
+        <v>3563428500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-39</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-10932636000</v>
+        <v>-10857015000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1319648000</v>
+        <v>1310520000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1176753600</v>
+        <v>-1168614000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>459407520</v>
+        <v>456229800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-28</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-9166696000</v>
+        <v>-9103290000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1968947200</v>
+        <v>1955328000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-26</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1276132000</v>
+        <v>-1267305000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1374700800</v>
+        <v>1365192000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-24</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-845222400</v>
+        <v>-839376000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>918086400</v>
+        <v>911736000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-23</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1834148800</v>
+        <v>-1821462000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1404453600</v>
+        <v>1394739000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-21</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-936150600</v>
+        <v>-929675250</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>26</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>970912800</v>
+        <v>964197000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1897095200</v>
+        <v>-1883973000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>10590580000</v>
+        <v>10517325000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-737140800</v>
+        <v>-817668000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.07%→0.81%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1415383200</v>
+        <v>1405593000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-823363200</v>
+        <v>-732042000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1185254400</v>
+        <v>1177056000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-9</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-797860800</v>
+        <v>-792342000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1411740000</v>
+        <v>1401975000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-465520000</v>
+        <v>-462300000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>824274000</v>
+        <v>818572500</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-3</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-470276400</v>
+        <v>-467023500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,531억   ·   현금 131억(3.6%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 4종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,489억   ·   현금 87억(2.5%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1419,7 +1419,7 @@
         <v>66</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>726580800</v>
+        <v>725204700</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>-607</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-5070246720</v>
+        <v>-5060643980</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>37</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1027593600</v>
+        <v>1025647400</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>-185</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-681806400</v>
+        <v>-680515100</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>29</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1038153600</v>
+        <v>1036187400</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>-32</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-393676800</v>
+        <v>-392931200</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>14</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>737721600</v>
+        <v>736324400</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-630115200</v>
+        <v>-628921800</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>-10</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-156024000</v>
+        <v>-155728500</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,613억   ·   현금 126억(4.6%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 9종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 84억(3.1%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 9종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
         <v>97</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>521297400</v>
+        <v>519784200</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>-224</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1497059200</v>
+        <v>-1492713600</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>77</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2594291700</v>
+        <v>2586761100</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>-150</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2113507500</v>
+        <v>-2107372500</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>60</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>4026516000</v>
+        <v>4014828000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>-105</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1526479500</v>
+        <v>-1522048500</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5572287500</v>
+        <v>5556112500</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>-99</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1320564960</v>
+        <v>-1316731680</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>23</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2454700300</v>
+        <v>2447574900</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>-96</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-8856681600</v>
+        <v>-8830972800</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>623820600</v>
+        <v>622009800</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>-65</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1945908250</v>
+        <v>-1940259750</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3167677500</v>
+        <v>3158482500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>-63</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2135624400</v>
+        <v>-2129425200</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>516887800</v>
+        <v>515387400</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>-50</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1598480000</v>
+        <v>-1593840000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1567475000</v>
+        <v>1562925000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>-30</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-686244000</v>
+        <v>-684252000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,000억   ·   현금 14억(0.7%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 7종목  /  매도 8종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,974억   ·   현금 9억(0.5%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2526,7 +2526,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 2억(0.9%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 8종목  /  매도 11종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 1억(0.3%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 8종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -2622,11 +2622,11 @@
         <v>274</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>192567200</v>
+        <v>189882000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>6.83%→7.51%</t>
+          <t>6.67%→7.34%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2643,11 +2643,11 @@
         <v>-92</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-149408000</v>
+        <v>-150052000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>5.61%→5.06%</t>
+          <t>5.58%→5.04%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2666,11 +2666,11 @@
         <v>48</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>149856000</v>
+        <v>146328000</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.42%</t>
+          <t>0.86%→1.38%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2687,11 +2687,11 @@
         <v>-53</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-166764500</v>
+        <v>-181419000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>4.23%→3.62%</t>
+          <t>4.56%→3.91%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2710,11 +2710,11 @@
         <v>39</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>185913000</v>
+        <v>186186000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.99%</t>
+          <t>0.32%→0.98%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2731,11 +2731,11 @@
         <v>-41</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-31024700</v>
+        <v>-30651600</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.83%</t>
+          <t>0.92%→0.81%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2754,11 +2754,11 @@
         <v>26</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>40131000</v>
+        <v>38675000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>1.62%→1.77%</t>
+          <t>1.55%→1.69%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2775,11 +2775,11 @@
         <v>-18</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-54369000</v>
+        <v>-53487000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.78%→2.58%</t>
+          <t>2.71%→2.51%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2798,7 +2798,7 @@
         <v>25</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>63700000</v>
+        <v>64312500</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2819,11 +2819,11 @@
         <v>-13</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-29393000</v>
+        <v>-29484000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.13%→2.02%</t>
+          <t>2.11%→2.01%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2842,11 +2842,11 @@
         <v>12</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>43764000</v>
+        <v>46200000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>1.14%→1.29%</t>
+          <t>1.19%→1.36%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2863,11 +2863,11 @@
         <v>-12</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-58380000</v>
+        <v>-55944000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>1.89%→1.68%</t>
+          <t>1.79%→1.59%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2886,11 +2886,11 @@
         <v>4</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>24472000</v>
+        <v>24360000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>1.74%→1.82%</t>
+          <t>1.71%→1.80%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2907,11 +2907,11 @@
         <v>-9</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-22396500</v>
+        <v>-22270500</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.91%</t>
+          <t>0.98%→0.90%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2930,11 +2930,11 @@
         <v>3</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>98700000</v>
+        <v>95550000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.83%→1.18%</t>
+          <t>0.79%→1.13%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2951,11 +2951,11 @@
         <v>-8</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-85344000</v>
+        <v>-86800000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>3.72%→3.41%</t>
+          <t>3.74%→3.43%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2979,11 +2979,11 @@
         <v>-7</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-58849000</v>
+        <v>-58212000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.35%</t>
+          <t>2.52%→2.31%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -3000,23 +3000,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-43260000</v>
+        <v>-66710000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.19%</t>
+          <t>1.80%→1.57%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>11→6</t>
+          <t>38→33</t>
         </is>
       </c>
     </row>
@@ -3028,30 +3028,30 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-66710000</v>
+        <v>-42315000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>1.82%→1.58%</t>
+          <t>0.33%→0.18%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>38→33</t>
+          <t>11→6</t>
         </is>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 500억   ·   현금 12억(2.5%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 493억   ·   현금 8억(1.7%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260911.xlsx
+++ b/reports/pdf_rolling5_20260911.xlsx
@@ -2526,7 +2526,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 1억(0.3%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 8종목  /  매도 11종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 2억(0.6%)      오늘 2026-09-11  vs  5일전 2026-09-04      매수 8종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -3000,23 +3000,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-66710000</v>
+        <v>-42315000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.80%→1.57%</t>
+          <t>0.33%→0.18%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>38→33</t>
+          <t>11→6</t>
         </is>
       </c>
     </row>
@@ -3028,23 +3028,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-42315000</v>
+        <v>-66710000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.18%</t>
+          <t>1.80%→1.57%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>11→6</t>
+          <t>38→33</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260911.xlsx
+++ b/reports/pdf_rolling5_20260911.xlsx
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-817668000</v>
+        <v>-732042000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-732042000</v>
+        <v>-817668000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.07%→0.81%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
